--- a/career_demo/career_jobs.xlsx
+++ b/career_demo/career_jobs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\Kirbs_rnbd\career_demo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_04DD3621D66A660E62355476585DCE3A871AE1AE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB1625C-C4C9-4F61-B417-929DDF2861C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10965" uniqueCount="5729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10966" uniqueCount="5730">
   <si>
     <t>job</t>
   </si>
@@ -22467,6 +22467,10 @@
 - 근무시간이 규칙적이며, 물리적 환경이 쾌적하여 육체적 스트레스는 심하지 않으나 정신적 스트레스는 평균에 비해 심한 것으로 나타났다.
 - 자연과학 연구원은 전문성을 바탕으로 업무에 대한 자율성이나 권한이 높다. 사회적으로 평판이 좋고 사회적인 기여나 소명에 대한 의식이 높은 편으로 나타났다.
 - 고용에서 성별이나 연령에 따른 차별이 없는 편이다.</t>
+  </si>
+  <si>
+    <t>index</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -22842,6 +22846,9 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>5729</v>
+      </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
